--- a/NE_year1_awardees.xlsx
+++ b/NE_year1_awardees.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
   <si>
     <t xml:space="preserve">note</t>
   </si>
@@ -392,6 +392,12 @@
   </si>
   <si>
     <t xml:space="preserve">Southeast District Health Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOCAL_GOVT_OR_PUBLIC_HEALTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recipient name rule: a health department, or a body named Public Health &lt;place&gt;: a local public health body. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work.</t>
   </si>
   <si>
     <t xml:space="preserve">Chase Community Hospital</t>
@@ -3306,7 +3312,7 @@
         <v>195746.93</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="F24" t="s">
         <v>71</v>
@@ -3346,11 +3352,9 @@
         <v>80</v>
       </c>
       <c r="U24" t="s">
-        <v>81</v>
-      </c>
-      <c r="V24" t="s">
-        <v>82</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="V24"/>
       <c r="W24" t="s">
         <v>102</v>
       </c>
@@ -3370,10 +3374,10 @@
       <c r="AC24"/>
       <c r="AD24"/>
       <c r="AE24" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="AF24" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG24" t="s">
         <v>105</v>
@@ -3387,7 +3391,7 @@
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D25" t="n">
         <v>338714.13</v>
@@ -3472,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D26" t="n">
         <v>339996.26</v>
@@ -3557,7 +3561,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D27" t="n">
         <v>284957.28</v>
@@ -3642,7 +3646,7 @@
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D28" t="n">
         <v>309749.28</v>
@@ -3729,7 +3733,7 @@
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D29" t="n">
         <v>339999.92</v>
@@ -3816,7 +3820,7 @@
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" t="n">
         <v>118400</v>
@@ -3903,7 +3907,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D31" t="n">
         <v>279582.73</v>
@@ -3990,7 +3994,7 @@
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D32" t="n">
         <v>279582.73</v>
@@ -4077,7 +4081,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D33" t="n">
         <v>238083.71</v>
@@ -4164,7 +4168,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D34" t="n">
         <v>90000</v>
@@ -4249,7 +4253,7 @@
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D35" t="n">
         <v>778897.18</v>
@@ -4261,7 +4265,7 @@
         <v>73</v>
       </c>
       <c r="G35" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H35" t="s">
         <v>73</v>
@@ -4273,10 +4277,10 @@
         <v>74</v>
       </c>
       <c r="K35" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M35" t="s">
         <v>77</v>
@@ -4299,7 +4303,7 @@
       </c>
       <c r="V35"/>
       <c r="W35" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X35" t="s">
         <v>83</v>
@@ -4323,7 +4327,7 @@
         <v>97</v>
       </c>
       <c r="AG35" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36">
@@ -4334,7 +4338,7 @@
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D36" t="n">
         <v>278684.02</v>
@@ -4346,7 +4350,7 @@
         <v>73</v>
       </c>
       <c r="G36" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H36" t="s">
         <v>73</v>
@@ -4358,10 +4362,10 @@
         <v>74</v>
       </c>
       <c r="K36" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M36" t="s">
         <v>77</v>
@@ -4384,7 +4388,7 @@
       </c>
       <c r="V36"/>
       <c r="W36" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X36" t="s">
         <v>83</v>
@@ -4408,7 +4412,7 @@
         <v>97</v>
       </c>
       <c r="AG36" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37">
@@ -4419,7 +4423,7 @@
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D37" t="n">
         <v>200000</v>
@@ -4431,7 +4435,7 @@
         <v>73</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H37" t="s">
         <v>73</v>
@@ -4443,10 +4447,10 @@
         <v>74</v>
       </c>
       <c r="K37" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L37" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M37" t="s">
         <v>77</v>
@@ -4469,7 +4473,7 @@
       </c>
       <c r="V37"/>
       <c r="W37" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X37" t="s">
         <v>83</v>
@@ -4493,7 +4497,7 @@
         <v>97</v>
       </c>
       <c r="AG37" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38">
@@ -4504,7 +4508,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D38" t="n">
         <v>430601.57</v>
@@ -4516,7 +4520,7 @@
         <v>71</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H38" t="s">
         <v>73</v>
@@ -4528,10 +4532,10 @@
         <v>74</v>
       </c>
       <c r="K38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M38" t="s">
         <v>77</v>
@@ -4556,7 +4560,7 @@
         <v>82</v>
       </c>
       <c r="W38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X38" t="s">
         <v>83</v>
@@ -4580,7 +4584,7 @@
         <v>87</v>
       </c>
       <c r="AG38" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39">
@@ -4591,7 +4595,7 @@
         <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D39" t="n">
         <v>355311.03</v>
@@ -4603,7 +4607,7 @@
         <v>71</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H39" t="s">
         <v>73</v>
@@ -4615,10 +4619,10 @@
         <v>74</v>
       </c>
       <c r="K39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M39" t="s">
         <v>77</v>
@@ -4643,7 +4647,7 @@
         <v>82</v>
       </c>
       <c r="W39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X39" t="s">
         <v>83</v>
@@ -4667,7 +4671,7 @@
         <v>87</v>
       </c>
       <c r="AG39" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40">
@@ -4678,7 +4682,7 @@
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D40" t="n">
         <v>711629.63</v>
@@ -4690,7 +4694,7 @@
         <v>71</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H40" t="s">
         <v>73</v>
@@ -4702,10 +4706,10 @@
         <v>74</v>
       </c>
       <c r="K40" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M40" t="s">
         <v>77</v>
@@ -4730,7 +4734,7 @@
         <v>82</v>
       </c>
       <c r="W40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X40" t="s">
         <v>83</v>
@@ -4754,7 +4758,7 @@
         <v>87</v>
       </c>
       <c r="AG40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41">
@@ -4765,7 +4769,7 @@
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D41" t="n">
         <v>908475.54</v>
@@ -4777,7 +4781,7 @@
         <v>71</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
         <v>73</v>
@@ -4789,10 +4793,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L41" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M41" t="s">
         <v>77</v>
@@ -4817,7 +4821,7 @@
         <v>82</v>
       </c>
       <c r="W41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X41" t="s">
         <v>83</v>
@@ -4841,7 +4845,7 @@
         <v>87</v>
       </c>
       <c r="AG41" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42">
@@ -4852,7 +4856,7 @@
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D42" t="n">
         <v>195523.2</v>
@@ -4864,7 +4868,7 @@
         <v>73</v>
       </c>
       <c r="G42" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H42" t="s">
         <v>73</v>
@@ -4876,10 +4880,10 @@
         <v>74</v>
       </c>
       <c r="K42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L42" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M42" t="s">
         <v>77</v>
@@ -4902,7 +4906,7 @@
       </c>
       <c r="V42"/>
       <c r="W42" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X42" t="s">
         <v>83</v>
@@ -4926,7 +4930,7 @@
         <v>97</v>
       </c>
       <c r="AG42" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43">
@@ -4937,7 +4941,7 @@
         <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D43" t="n">
         <v>578673.7</v>
@@ -4949,7 +4953,7 @@
         <v>71</v>
       </c>
       <c r="G43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H43" t="s">
         <v>73</v>
@@ -4961,10 +4965,10 @@
         <v>74</v>
       </c>
       <c r="K43" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M43" t="s">
         <v>77</v>
@@ -4989,7 +4993,7 @@
         <v>82</v>
       </c>
       <c r="W43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X43" t="s">
         <v>83</v>
@@ -5013,7 +5017,7 @@
         <v>87</v>
       </c>
       <c r="AG43" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44">
@@ -5024,7 +5028,7 @@
         <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D44" t="n">
         <v>200000</v>
@@ -5036,7 +5040,7 @@
         <v>71</v>
       </c>
       <c r="G44" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H44" t="s">
         <v>73</v>
@@ -5048,10 +5052,10 @@
         <v>74</v>
       </c>
       <c r="K44" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M44" t="s">
         <v>77</v>
@@ -5076,7 +5080,7 @@
         <v>82</v>
       </c>
       <c r="W44" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X44" t="s">
         <v>83</v>
@@ -5100,7 +5104,7 @@
         <v>87</v>
       </c>
       <c r="AG44" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45">
@@ -5111,19 +5115,19 @@
         <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D45" t="n">
         <v>303276.49</v>
       </c>
       <c r="E45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F45" t="s">
         <v>71</v>
       </c>
       <c r="G45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H45" t="s">
         <v>73</v>
@@ -5135,10 +5139,10 @@
         <v>74</v>
       </c>
       <c r="K45" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M45" t="s">
         <v>77</v>
@@ -5161,7 +5165,7 @@
       </c>
       <c r="V45"/>
       <c r="W45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X45" t="s">
         <v>83</v>
@@ -5179,13 +5183,13 @@
       <c r="AC45"/>
       <c r="AD45"/>
       <c r="AE45" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AF45" t="s">
         <v>97</v>
       </c>
       <c r="AG45" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46">
@@ -5196,7 +5200,7 @@
         <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D46" t="n">
         <v>199950</v>
@@ -5208,7 +5212,7 @@
         <v>71</v>
       </c>
       <c r="G46" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H46" t="s">
         <v>73</v>
@@ -5220,10 +5224,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L46" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M46" t="s">
         <v>77</v>
@@ -5248,7 +5252,7 @@
         <v>82</v>
       </c>
       <c r="W46" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X46" t="s">
         <v>83</v>
@@ -5272,7 +5276,7 @@
         <v>87</v>
       </c>
       <c r="AG46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47">
@@ -5283,7 +5287,7 @@
         <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D47" t="n">
         <v>446741.33</v>
@@ -5295,7 +5299,7 @@
         <v>71</v>
       </c>
       <c r="G47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H47" t="s">
         <v>73</v>
@@ -5307,10 +5311,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L47" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M47" t="s">
         <v>77</v>
@@ -5335,7 +5339,7 @@
         <v>82</v>
       </c>
       <c r="W47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X47" t="s">
         <v>83</v>
@@ -5359,7 +5363,7 @@
         <v>87</v>
       </c>
       <c r="AG47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48">
@@ -5370,7 +5374,7 @@
         <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D48" t="n">
         <v>393220.57</v>
@@ -5382,7 +5386,7 @@
         <v>73</v>
       </c>
       <c r="G48" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H48" t="s">
         <v>73</v>
@@ -5394,10 +5398,10 @@
         <v>74</v>
       </c>
       <c r="K48" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L48" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M48" t="s">
         <v>77</v>
@@ -5420,7 +5424,7 @@
       </c>
       <c r="V48"/>
       <c r="W48" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X48" t="s">
         <v>83</v>
@@ -5444,7 +5448,7 @@
         <v>97</v>
       </c>
       <c r="AG48" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49">
@@ -5455,7 +5459,7 @@
         <v>48</v>
       </c>
       <c r="C49" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D49" t="n">
         <v>460239.4</v>
@@ -5467,7 +5471,7 @@
         <v>71</v>
       </c>
       <c r="G49" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H49" t="s">
         <v>73</v>
@@ -5479,10 +5483,10 @@
         <v>74</v>
       </c>
       <c r="K49" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M49" t="s">
         <v>77</v>
@@ -5507,7 +5511,7 @@
         <v>82</v>
       </c>
       <c r="W49" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X49" t="s">
         <v>83</v>
@@ -5531,7 +5535,7 @@
         <v>87</v>
       </c>
       <c r="AG49" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50">
@@ -5542,7 +5546,7 @@
         <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D50" t="n">
         <v>334176.13</v>
@@ -5554,7 +5558,7 @@
         <v>71</v>
       </c>
       <c r="G50" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H50" t="s">
         <v>73</v>
@@ -5566,10 +5570,10 @@
         <v>74</v>
       </c>
       <c r="K50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L50" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M50" t="s">
         <v>77</v>
@@ -5594,7 +5598,7 @@
         <v>82</v>
       </c>
       <c r="W50" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X50" t="s">
         <v>83</v>
@@ -5618,7 +5622,7 @@
         <v>87</v>
       </c>
       <c r="AG50" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51">
@@ -5629,7 +5633,7 @@
         <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D51" t="n">
         <v>221239.63</v>
@@ -5641,7 +5645,7 @@
         <v>71</v>
       </c>
       <c r="G51" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H51" t="s">
         <v>73</v>
@@ -5653,10 +5657,10 @@
         <v>74</v>
       </c>
       <c r="K51" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L51" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M51" t="s">
         <v>77</v>
@@ -5681,7 +5685,7 @@
         <v>82</v>
       </c>
       <c r="W51" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X51" t="s">
         <v>83</v>
@@ -5705,7 +5709,7 @@
         <v>87</v>
       </c>
       <c r="AG51" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52">
@@ -5716,7 +5720,7 @@
         <v>51</v>
       </c>
       <c r="C52" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D52" t="n">
         <v>18156856.12</v>
@@ -5728,7 +5732,7 @@
         <v>73</v>
       </c>
       <c r="G52" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H52" t="s">
         <v>73</v>
@@ -5740,10 +5744,10 @@
         <v>74</v>
       </c>
       <c r="K52" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L52" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M52" t="s">
         <v>77</v>
@@ -5768,33 +5772,33 @@
         <v>82</v>
       </c>
       <c r="W52" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X52" t="s">
         <v>83</v>
       </c>
       <c r="Y52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Z52" t="s">
         <v>73</v>
       </c>
       <c r="AA52" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AB52" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC52"/>
       <c r="AD52"/>
       <c r="AE52" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AF52" t="s">
         <v>87</v>
       </c>
       <c r="AG52" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53">
@@ -5805,19 +5809,19 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D53" t="n">
         <v>395048.53</v>
       </c>
       <c r="E53" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F53" t="s">
         <v>71</v>
       </c>
       <c r="G53" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H53" t="s">
         <v>73</v>
@@ -5829,10 +5833,10 @@
         <v>74</v>
       </c>
       <c r="K53" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L53" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M53" t="s">
         <v>77</v>
@@ -5855,7 +5859,7 @@
       </c>
       <c r="V53"/>
       <c r="W53" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X53" t="s">
         <v>83</v>
@@ -5873,13 +5877,13 @@
       <c r="AC53"/>
       <c r="AD53"/>
       <c r="AE53" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AF53" t="s">
         <v>97</v>
       </c>
       <c r="AG53" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54">
@@ -5890,7 +5894,7 @@
         <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D54" t="n">
         <v>479692.57</v>
@@ -5902,7 +5906,7 @@
         <v>73</v>
       </c>
       <c r="G54" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H54" t="s">
         <v>73</v>
@@ -5914,10 +5918,10 @@
         <v>74</v>
       </c>
       <c r="K54" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L54" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M54" t="s">
         <v>77</v>
@@ -5940,7 +5944,7 @@
       </c>
       <c r="V54"/>
       <c r="W54" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X54" t="s">
         <v>83</v>
@@ -5964,7 +5968,7 @@
         <v>97</v>
       </c>
       <c r="AG54" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55">
@@ -5975,7 +5979,7 @@
         <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D55" t="n">
         <v>311698.7</v>
@@ -5987,7 +5991,7 @@
         <v>73</v>
       </c>
       <c r="G55" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H55" t="s">
         <v>73</v>
@@ -5999,10 +6003,10 @@
         <v>74</v>
       </c>
       <c r="K55" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L55" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M55" t="s">
         <v>77</v>
@@ -6025,7 +6029,7 @@
       </c>
       <c r="V55"/>
       <c r="W55" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X55" t="s">
         <v>83</v>
@@ -6049,7 +6053,7 @@
         <v>97</v>
       </c>
       <c r="AG55" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56">
@@ -6060,7 +6064,7 @@
         <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D56" t="n">
         <v>736148.14</v>
@@ -6072,7 +6076,7 @@
         <v>73</v>
       </c>
       <c r="G56" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H56" t="s">
         <v>73</v>
@@ -6084,10 +6088,10 @@
         <v>74</v>
       </c>
       <c r="K56" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L56" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M56" t="s">
         <v>77</v>
@@ -6110,7 +6114,7 @@
       </c>
       <c r="V56"/>
       <c r="W56" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X56" t="s">
         <v>83</v>
@@ -6134,7 +6138,7 @@
         <v>97</v>
       </c>
       <c r="AG56" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57">
@@ -6145,7 +6149,7 @@
         <v>56</v>
       </c>
       <c r="C57" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D57" t="n">
         <v>200000</v>
@@ -6157,7 +6161,7 @@
         <v>71</v>
       </c>
       <c r="G57" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H57" t="s">
         <v>73</v>
@@ -6169,10 +6173,10 @@
         <v>74</v>
       </c>
       <c r="K57" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L57" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M57" t="s">
         <v>77</v>
@@ -6197,7 +6201,7 @@
         <v>82</v>
       </c>
       <c r="W57" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X57" t="s">
         <v>83</v>
@@ -6221,7 +6225,7 @@
         <v>87</v>
       </c>
       <c r="AG57" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58">
@@ -6232,7 +6236,7 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D58" t="n">
         <v>414693.75</v>
@@ -6244,7 +6248,7 @@
         <v>73</v>
       </c>
       <c r="G58" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H58" t="s">
         <v>73</v>
@@ -6256,10 +6260,10 @@
         <v>74</v>
       </c>
       <c r="K58" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L58" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M58" t="s">
         <v>77</v>
@@ -6282,7 +6286,7 @@
       </c>
       <c r="V58"/>
       <c r="W58" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="X58" t="s">
         <v>83</v>
@@ -6306,7 +6310,7 @@
         <v>97</v>
       </c>
       <c r="AG58" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59">
@@ -6327,7 +6331,7 @@
         <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H59" t="s">
         <v>73</v>
@@ -6339,10 +6343,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L59" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M59" t="s">
         <v>77</v>
@@ -6358,16 +6362,16 @@
       <c r="R59"/>
       <c r="S59"/>
       <c r="T59" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U59" t="s">
         <v>118</v>
       </c>
       <c r="V59" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X59" t="s">
         <v>83</v>
@@ -6382,22 +6386,22 @@
         <v>110</v>
       </c>
       <c r="AB59" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC59" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AE59" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF59" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG59" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60">
@@ -6408,7 +6412,7 @@
         <v>59</v>
       </c>
       <c r="C60" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D60"/>
       <c r="E60" t="s">
@@ -6418,7 +6422,7 @@
         <v>73</v>
       </c>
       <c r="G60" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H60" t="s">
         <v>73</v>
@@ -6430,10 +6434,10 @@
         <v>74</v>
       </c>
       <c r="K60" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L60" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M60" t="s">
         <v>77</v>
@@ -6449,16 +6453,16 @@
       <c r="R60"/>
       <c r="S60"/>
       <c r="T60" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U60" t="s">
         <v>118</v>
       </c>
       <c r="V60" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W60" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X60" t="s">
         <v>83</v>
@@ -6473,22 +6477,22 @@
         <v>110</v>
       </c>
       <c r="AB60" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC60" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD60" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AE60" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF60" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG60" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61">
@@ -6499,7 +6503,7 @@
         <v>60</v>
       </c>
       <c r="C61" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D61"/>
       <c r="E61" t="s">
@@ -6509,7 +6513,7 @@
         <v>73</v>
       </c>
       <c r="G61" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H61" t="s">
         <v>73</v>
@@ -6521,10 +6525,10 @@
         <v>74</v>
       </c>
       <c r="K61" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L61" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M61" t="s">
         <v>77</v>
@@ -6540,16 +6544,16 @@
       <c r="R61"/>
       <c r="S61"/>
       <c r="T61" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U61" t="s">
         <v>118</v>
       </c>
       <c r="V61" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W61" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X61" t="s">
         <v>83</v>
@@ -6564,22 +6568,22 @@
         <v>110</v>
       </c>
       <c r="AB61" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC61" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD61" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AE61" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF61" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG61" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62">
@@ -6590,7 +6594,7 @@
         <v>61</v>
       </c>
       <c r="C62" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D62"/>
       <c r="E62" t="s">
@@ -6600,7 +6604,7 @@
         <v>73</v>
       </c>
       <c r="G62" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H62" t="s">
         <v>73</v>
@@ -6612,10 +6616,10 @@
         <v>74</v>
       </c>
       <c r="K62" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L62" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M62" t="s">
         <v>77</v>
@@ -6631,16 +6635,16 @@
       <c r="R62"/>
       <c r="S62"/>
       <c r="T62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U62" t="s">
         <v>118</v>
       </c>
       <c r="V62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W62" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X62" t="s">
         <v>83</v>
@@ -6655,22 +6659,22 @@
         <v>110</v>
       </c>
       <c r="AB62" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC62" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD62" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AE62" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG62" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63">
@@ -6681,7 +6685,7 @@
         <v>62</v>
       </c>
       <c r="C63" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D63"/>
       <c r="E63" t="s">
@@ -6691,7 +6695,7 @@
         <v>73</v>
       </c>
       <c r="G63" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H63" t="s">
         <v>73</v>
@@ -6703,10 +6707,10 @@
         <v>74</v>
       </c>
       <c r="K63" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L63" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M63" t="s">
         <v>77</v>
@@ -6722,16 +6726,16 @@
       <c r="R63"/>
       <c r="S63"/>
       <c r="T63" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U63" t="s">
         <v>118</v>
       </c>
       <c r="V63" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X63" t="s">
         <v>83</v>
@@ -6746,22 +6750,22 @@
         <v>110</v>
       </c>
       <c r="AB63" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC63" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD63" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AE63" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF63" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG63" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64">
@@ -6772,7 +6776,7 @@
         <v>63</v>
       </c>
       <c r="C64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D64"/>
       <c r="E64" t="s">
@@ -6782,7 +6786,7 @@
         <v>73</v>
       </c>
       <c r="G64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H64" t="s">
         <v>73</v>
@@ -6794,10 +6798,10 @@
         <v>74</v>
       </c>
       <c r="K64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M64" t="s">
         <v>77</v>
@@ -6813,16 +6817,16 @@
       <c r="R64"/>
       <c r="S64"/>
       <c r="T64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U64" t="s">
         <v>118</v>
       </c>
       <c r="V64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X64" t="s">
         <v>83</v>
@@ -6837,22 +6841,22 @@
         <v>110</v>
       </c>
       <c r="AB64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AE64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65">
@@ -6863,7 +6867,7 @@
         <v>64</v>
       </c>
       <c r="C65" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D65"/>
       <c r="E65" t="s">
@@ -6873,7 +6877,7 @@
         <v>73</v>
       </c>
       <c r="G65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H65" t="s">
         <v>73</v>
@@ -6885,10 +6889,10 @@
         <v>74</v>
       </c>
       <c r="K65" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L65" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M65" t="s">
         <v>77</v>
@@ -6904,16 +6908,16 @@
       <c r="R65"/>
       <c r="S65"/>
       <c r="T65" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U65" t="s">
         <v>118</v>
       </c>
       <c r="V65" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W65" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X65" t="s">
         <v>83</v>
@@ -6928,22 +6932,22 @@
         <v>110</v>
       </c>
       <c r="AB65" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC65" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD65" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AE65" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF65" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG65" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66">
@@ -6954,7 +6958,7 @@
         <v>65</v>
       </c>
       <c r="C66" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D66"/>
       <c r="E66" t="s">
@@ -6964,7 +6968,7 @@
         <v>73</v>
       </c>
       <c r="G66" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H66" t="s">
         <v>73</v>
@@ -6976,10 +6980,10 @@
         <v>74</v>
       </c>
       <c r="K66" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L66" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M66" t="s">
         <v>77</v>
@@ -6995,16 +6999,16 @@
       <c r="R66"/>
       <c r="S66"/>
       <c r="T66" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U66" t="s">
         <v>118</v>
       </c>
       <c r="V66" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W66" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X66" t="s">
         <v>83</v>
@@ -7019,22 +7023,22 @@
         <v>110</v>
       </c>
       <c r="AB66" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC66" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD66" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AE66" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF66" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG66" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67">
@@ -7045,7 +7049,7 @@
         <v>66</v>
       </c>
       <c r="C67" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D67"/>
       <c r="E67" t="s">
@@ -7055,7 +7059,7 @@
         <v>73</v>
       </c>
       <c r="G67" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H67" t="s">
         <v>73</v>
@@ -7067,10 +7071,10 @@
         <v>74</v>
       </c>
       <c r="K67" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L67" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M67" t="s">
         <v>77</v>
@@ -7086,16 +7090,16 @@
       <c r="R67"/>
       <c r="S67"/>
       <c r="T67" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U67" t="s">
         <v>118</v>
       </c>
       <c r="V67" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X67" t="s">
         <v>83</v>
@@ -7110,22 +7114,22 @@
         <v>110</v>
       </c>
       <c r="AB67" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC67" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD67" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AE67" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF67" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG67" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68">
@@ -7136,7 +7140,7 @@
         <v>67</v>
       </c>
       <c r="C68" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D68"/>
       <c r="E68" t="s">
@@ -7146,7 +7150,7 @@
         <v>73</v>
       </c>
       <c r="G68" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H68" t="s">
         <v>73</v>
@@ -7158,10 +7162,10 @@
         <v>74</v>
       </c>
       <c r="K68" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L68" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M68" t="s">
         <v>77</v>
@@ -7177,16 +7181,16 @@
       <c r="R68"/>
       <c r="S68"/>
       <c r="T68" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U68" t="s">
         <v>118</v>
       </c>
       <c r="V68" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W68" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X68" t="s">
         <v>83</v>
@@ -7201,22 +7205,22 @@
         <v>110</v>
       </c>
       <c r="AB68" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC68" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD68" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AE68" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF68" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG68" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69">
@@ -7227,7 +7231,7 @@
         <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D69"/>
       <c r="E69" t="s">
@@ -7237,7 +7241,7 @@
         <v>73</v>
       </c>
       <c r="G69" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H69" t="s">
         <v>73</v>
@@ -7249,10 +7253,10 @@
         <v>74</v>
       </c>
       <c r="K69" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L69" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M69" t="s">
         <v>77</v>
@@ -7268,16 +7272,16 @@
       <c r="R69"/>
       <c r="S69"/>
       <c r="T69" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U69" t="s">
         <v>118</v>
       </c>
       <c r="V69" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W69" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X69" t="s">
         <v>83</v>
@@ -7292,22 +7296,22 @@
         <v>110</v>
       </c>
       <c r="AB69" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC69" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD69" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AE69" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF69" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG69" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="70">
@@ -7318,7 +7322,7 @@
         <v>69</v>
       </c>
       <c r="C70" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D70"/>
       <c r="E70" t="s">
@@ -7328,7 +7332,7 @@
         <v>73</v>
       </c>
       <c r="G70" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H70" t="s">
         <v>73</v>
@@ -7340,10 +7344,10 @@
         <v>74</v>
       </c>
       <c r="K70" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L70" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M70" t="s">
         <v>77</v>
@@ -7359,16 +7363,16 @@
       <c r="R70"/>
       <c r="S70"/>
       <c r="T70" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U70" t="s">
         <v>118</v>
       </c>
       <c r="V70" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W70" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X70" t="s">
         <v>83</v>
@@ -7383,22 +7387,22 @@
         <v>110</v>
       </c>
       <c r="AB70" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC70" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD70" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AE70" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF70" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG70" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71">
@@ -7409,7 +7413,7 @@
         <v>70</v>
       </c>
       <c r="C71" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D71"/>
       <c r="E71" t="s">
@@ -7419,7 +7423,7 @@
         <v>73</v>
       </c>
       <c r="G71" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H71" t="s">
         <v>73</v>
@@ -7431,10 +7435,10 @@
         <v>74</v>
       </c>
       <c r="K71" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L71" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M71" t="s">
         <v>77</v>
@@ -7450,16 +7454,16 @@
       <c r="R71"/>
       <c r="S71"/>
       <c r="T71" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U71" t="s">
         <v>118</v>
       </c>
       <c r="V71" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W71" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X71" t="s">
         <v>83</v>
@@ -7474,22 +7478,22 @@
         <v>110</v>
       </c>
       <c r="AB71" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC71" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD71" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AE71" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF71" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG71" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72">
@@ -7500,7 +7504,7 @@
         <v>71</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D72"/>
       <c r="E72" t="s">
@@ -7510,7 +7514,7 @@
         <v>73</v>
       </c>
       <c r="G72" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H72" t="s">
         <v>73</v>
@@ -7522,10 +7526,10 @@
         <v>74</v>
       </c>
       <c r="K72" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L72" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M72" t="s">
         <v>77</v>
@@ -7541,16 +7545,16 @@
       <c r="R72"/>
       <c r="S72"/>
       <c r="T72" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U72" t="s">
         <v>118</v>
       </c>
       <c r="V72" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W72" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X72" t="s">
         <v>83</v>
@@ -7565,22 +7569,22 @@
         <v>110</v>
       </c>
       <c r="AB72" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC72" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD72" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AE72" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF72" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG72" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73">
@@ -7591,7 +7595,7 @@
         <v>72</v>
       </c>
       <c r="C73" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D73"/>
       <c r="E73" t="s">
@@ -7601,7 +7605,7 @@
         <v>73</v>
       </c>
       <c r="G73" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H73" t="s">
         <v>73</v>
@@ -7613,10 +7617,10 @@
         <v>74</v>
       </c>
       <c r="K73" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L73" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M73" t="s">
         <v>77</v>
@@ -7632,16 +7636,16 @@
       <c r="R73"/>
       <c r="S73"/>
       <c r="T73" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U73" t="s">
         <v>118</v>
       </c>
       <c r="V73" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W73" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X73" t="s">
         <v>83</v>
@@ -7656,22 +7660,22 @@
         <v>110</v>
       </c>
       <c r="AB73" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC73" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD73" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AE73" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF73" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG73" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74">
@@ -7682,7 +7686,7 @@
         <v>73</v>
       </c>
       <c r="C74" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D74"/>
       <c r="E74" t="s">
@@ -7692,7 +7696,7 @@
         <v>73</v>
       </c>
       <c r="G74" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H74" t="s">
         <v>73</v>
@@ -7704,10 +7708,10 @@
         <v>74</v>
       </c>
       <c r="K74" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L74" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M74" t="s">
         <v>77</v>
@@ -7723,16 +7727,16 @@
       <c r="R74"/>
       <c r="S74"/>
       <c r="T74" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U74" t="s">
         <v>118</v>
       </c>
       <c r="V74" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W74" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X74" t="s">
         <v>83</v>
@@ -7747,22 +7751,22 @@
         <v>110</v>
       </c>
       <c r="AB74" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC74" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD74" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AE74" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF74" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG74" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="75">
@@ -7773,7 +7777,7 @@
         <v>74</v>
       </c>
       <c r="C75" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D75"/>
       <c r="E75" t="s">
@@ -7783,7 +7787,7 @@
         <v>73</v>
       </c>
       <c r="G75" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H75" t="s">
         <v>73</v>
@@ -7795,10 +7799,10 @@
         <v>74</v>
       </c>
       <c r="K75" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L75" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M75" t="s">
         <v>77</v>
@@ -7814,16 +7818,16 @@
       <c r="R75"/>
       <c r="S75"/>
       <c r="T75" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U75" t="s">
         <v>118</v>
       </c>
       <c r="V75" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W75" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X75" t="s">
         <v>83</v>
@@ -7838,22 +7842,22 @@
         <v>110</v>
       </c>
       <c r="AB75" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC75" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD75" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AE75" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF75" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG75" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76">
@@ -7864,7 +7868,7 @@
         <v>75</v>
       </c>
       <c r="C76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D76"/>
       <c r="E76" t="s">
@@ -7874,7 +7878,7 @@
         <v>73</v>
       </c>
       <c r="G76" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H76" t="s">
         <v>73</v>
@@ -7886,10 +7890,10 @@
         <v>74</v>
       </c>
       <c r="K76" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L76" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M76" t="s">
         <v>77</v>
@@ -7905,16 +7909,16 @@
       <c r="R76"/>
       <c r="S76"/>
       <c r="T76" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U76" t="s">
         <v>118</v>
       </c>
       <c r="V76" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W76" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X76" t="s">
         <v>83</v>
@@ -7929,22 +7933,22 @@
         <v>110</v>
       </c>
       <c r="AB76" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC76" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD76" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AE76" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF76" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG76" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="77">
@@ -7955,7 +7959,7 @@
         <v>76</v>
       </c>
       <c r="C77" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D77"/>
       <c r="E77" t="s">
@@ -7965,7 +7969,7 @@
         <v>73</v>
       </c>
       <c r="G77" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H77" t="s">
         <v>73</v>
@@ -7977,10 +7981,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L77" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M77" t="s">
         <v>77</v>
@@ -7996,16 +8000,16 @@
       <c r="R77"/>
       <c r="S77"/>
       <c r="T77" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U77" t="s">
         <v>118</v>
       </c>
       <c r="V77" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W77" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X77" t="s">
         <v>83</v>
@@ -8020,22 +8024,22 @@
         <v>110</v>
       </c>
       <c r="AB77" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC77" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD77" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AE77" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF77" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG77" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78">
@@ -8046,7 +8050,7 @@
         <v>77</v>
       </c>
       <c r="C78" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D78"/>
       <c r="E78" t="s">
@@ -8056,7 +8060,7 @@
         <v>73</v>
       </c>
       <c r="G78" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H78" t="s">
         <v>73</v>
@@ -8068,10 +8072,10 @@
         <v>74</v>
       </c>
       <c r="K78" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L78" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M78" t="s">
         <v>77</v>
@@ -8087,16 +8091,16 @@
       <c r="R78"/>
       <c r="S78"/>
       <c r="T78" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U78" t="s">
         <v>118</v>
       </c>
       <c r="V78" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W78" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X78" t="s">
         <v>83</v>
@@ -8111,22 +8115,22 @@
         <v>110</v>
       </c>
       <c r="AB78" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC78" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD78" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AE78" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF78" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG78" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79">
@@ -8137,7 +8141,7 @@
         <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D79"/>
       <c r="E79" t="s">
@@ -8147,7 +8151,7 @@
         <v>73</v>
       </c>
       <c r="G79" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H79" t="s">
         <v>73</v>
@@ -8159,10 +8163,10 @@
         <v>74</v>
       </c>
       <c r="K79" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L79" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M79" t="s">
         <v>77</v>
@@ -8178,16 +8182,16 @@
       <c r="R79"/>
       <c r="S79"/>
       <c r="T79" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="U79" t="s">
         <v>118</v>
       </c>
       <c r="V79" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="W79" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="X79" t="s">
         <v>83</v>
@@ -8202,22 +8206,22 @@
         <v>110</v>
       </c>
       <c r="AB79" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AC79" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD79" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AE79" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF79" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG79" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -8233,15 +8237,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B2" t="n">
         <v>1852376.73</v>
@@ -8249,7 +8253,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B3" t="n">
         <v>6594460.94</v>
@@ -8257,7 +8261,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B4" t="n">
         <v>27690777.23</v>
@@ -8265,7 +8269,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B5" t="n">
         <v>36137614.9</v>
@@ -8273,7 +8277,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B6" t="n">
         <v>218529075</v>
@@ -8281,7 +8285,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B7" t="n">
         <v>16.54</v>
@@ -8289,7 +8293,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B8" t="n">
         <v>18156856.12</v>
@@ -8297,7 +8301,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B9" t="n">
         <v>6990996.01</v>
@@ -8305,7 +8309,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B10" t="n">
         <v>18156856.12</v>
@@ -8313,7 +8317,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -8321,15 +8325,15 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B12" t="n">
-        <v>9411695.59</v>
+        <v>9215948.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B13" t="n">
         <v>39</v>
